--- a/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230301_20230901.xlsx
+++ b/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230301_20230901.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,10 +799,10 @@
         <v>-19.51219512195122</v>
       </c>
       <c r="H9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
@@ -840,10 +840,10 @@
         <v>-19.51219512195122</v>
       </c>
       <c r="H10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
@@ -980,31 +980,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60.97560975609756</v>
+        <v>59.34959349593496</v>
       </c>
       <c r="C14" t="n">
-        <v>37.39837398373984</v>
+        <v>39.83739837398374</v>
       </c>
       <c r="D14" t="n">
-        <v>73.45781099010526</v>
+        <v>86.87317153176926</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>INE463V01026</t>
+          <t>INE732I01013</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>-23.57723577235772</v>
+        <v>-19.51219512195122</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I14" t="n">
         <v>55</v>
@@ -1021,34 +1021,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59.34959349593496</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="C15" t="n">
-        <v>40.65040650406504</v>
+        <v>37.39837398373984</v>
       </c>
       <c r="D15" t="n">
-        <v>86.85655480051004</v>
+        <v>73.45781099010526</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>INE732I01013</t>
+          <t>INE463V01026</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>-18.69918699186992</v>
+        <v>-23.57723577235772</v>
       </c>
       <c r="H15" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J15" t="n">
         <v>14</v>
